--- a/public/form/補撥明細_範本.xlsx
+++ b/public/form/補撥明細_範本.xlsx
@@ -88,14 +88,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
@@ -103,7 +103,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="0"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
@@ -450,7 +450,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.375" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.125" style="2" customWidth="1"/>
@@ -462,7 +462,7 @@
     <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,7 +474,7 @@
       <c r="F1" s="4"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -485,7 +485,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="9" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>

--- a/public/form/補撥明細_範本.xlsx
+++ b/public/form/補撥明細_範本.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>申請門市</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,14 +38,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>商品類別</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>單位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>申請單號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>商品名稱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -54,15 +58,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>單位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>申請單號</t>
+    <t>DEP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PROD_NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QTY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>內容置左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>置中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INPUT_DATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORDER_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHOP_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已下有內容才畫格線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已下有內容才畫格線</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.5公分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2公分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -124,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -132,42 +180,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,66 +527,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="35.125" style="2" customWidth="1"/>
-    <col min="4" max="5" width="7.5" style="9" customWidth="1"/>
-    <col min="6" max="6" width="18.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="7.5" style="8" customWidth="1"/>
+    <col min="5" max="5" width="1.5" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.5" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="H1" s="6"/>
+      <c r="G1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="C4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>8</v>
-      </c>
+    <row r="5" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="I5" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="F7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.59055118110236227" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"微軟正黑體,粗體"&amp;16門市補撥單明細</oddHeader>
   </headerFooter>

--- a/public/form/補撥明細_範本.xlsx
+++ b/public/form/補撥明細_範本.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>申請門市</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,62 +55,6 @@
   </si>
   <si>
     <t>數量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROD_NAME</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>內容置左</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>置中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INPUT_DATE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORDER_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>USER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHOP_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已下有內容才畫格線</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已下有內容才畫格線</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7.5公分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2公分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -201,7 +145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -240,12 +184,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
@@ -544,34 +482,23 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D1" s="11"/>
       <c r="E1" s="4"/>
       <c r="F1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="G1" s="11"/>
       <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="5"/>
       <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -599,101 +526,6 @@
       <c r="I3" s="12" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="D5" s="14">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="14">
-        <v>1.3</v>
-      </c>
-      <c r="I5" s="14">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="F7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/public/form/補撥明細_範本.xlsx
+++ b/public/form/補撥明細_範本.xlsx
@@ -62,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -79,14 +79,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體"/>
@@ -97,6 +89,21 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -145,45 +152,51 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,60 +483,68 @@
   <cols>
     <col min="1" max="1" width="20.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="7.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="1.5" style="7" customWidth="1"/>
+    <col min="3" max="4" width="7.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="1.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="20.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="35.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.5" style="8" customWidth="1"/>
+    <col min="8" max="9" width="7.5" style="6" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="10" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="I1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="10" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="7" t="s">
         <v>4</v>
       </c>
     </row>
